--- a/reports/history/build-10/Backend_Test_Report.xlsx
+++ b/reports/history/build-10/Backend_Test_Report.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16 15:07:17</t>
+          <t>2026-06-22 09:26:19</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>6</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>6</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8">
@@ -592,11 +592,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -643,12 +643,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>Access Control (Basic Validation)</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Verify rules on /workers/{workerId} to make points, ratings, and badges read-only client-side</t>
+          <t>Block client write on /workers/{workerId}/points - Verify rule executes correctly under normal inputs</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>15:07:17</t>
+          <t>09:26:19</t>
         </is>
       </c>
     </row>
@@ -675,12 +675,12 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>Access Control (Basic Validation)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Verify rules on /notifications/{notifId} to restrict read/write access to recipient or admin</t>
+          <t>Block client write on /workers/{workerId}/rating - Verify rule executes correctly under normal inputs</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>15:07:17</t>
+          <t>09:26:19</t>
         </is>
       </c>
     </row>
@@ -707,12 +707,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>State Machine</t>
+          <t>Access Control (Basic Validation)</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Verify Cloud function trigger handles Verification Pending -&gt; Resolved transition to award points</t>
+          <t>Block client write on /workers/{workerId}/badges - Verify rule executes correctly under normal inputs</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>15:07:17</t>
+          <t>09:26:19</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Access Control (Basic Validation)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Verify zero rating protection in functions to prevent division-by-zero errors (NaN values)</t>
+          <t>Restrict read on /notifications to recipient UID - Verify rule executes correctly under normal inputs</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>15:07:17</t>
+          <t>09:26:19</t>
         </is>
       </c>
     </row>
@@ -771,12 +771,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Access Control (Basic Validation)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Verify timeline validation to check resolvedAt is greater than acceptedAt before rating</t>
+          <t>Restrict write on /notifications to recipient UID - Verify rule executes correctly under normal inputs</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>15:07:17</t>
+          <t>09:26:19</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>Access Control (Basic Validation)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Verify complaints creation rules to check request citizenId matches authenticated user UID</t>
+          <t>Allow admin write on /notifications for all - Verify rule executes correctly under normal inputs</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -823,7 +823,9543 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>15:07:17</t>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TC_B007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Allow citizen create on /complaints - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>TC_B008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Enforce citizenId matches auth.uid on /complaints creation - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>TC_B009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/status - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>TC_B010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/assignedWorkerId - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>TC_B011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Block public write on /leaderboard - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>TC_B012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Allow public read on /leaderboard - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>TC_B013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Block worker write on /workers/{otherId} - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>TC_B014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on worker profile details to auth users - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>TC_B015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Block unauthenticated users from Firestore reads/writes - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>TC_B016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved awards points - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>TC_B017</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved updates leaderboard - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>TC_B018</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Award points function handles worker rating calculation - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>TC_B019</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Rating calculation protects against division-by-zero - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>TC_B020</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: resolvedAt is after acceptedAt - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TC_B021</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: acceptedAt is after createdAt - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>TC_B022</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets assignedWorkerId - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TC_B023</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets status to In Progress - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>TC_B024</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Task rejection sets status back to In Progress - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TC_B025</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Auto-archive functions run on scheduled cron - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>TC_B026</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Verify complaint record requires mandatory title/description - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TC_B027</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Verify worker points count is non-negative - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>TC_B028</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Verify rating value is restricted between 1 and 5 - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TC_B029</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Firestore inputs sanitized for XSS/injection payloads - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>TC_B030</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Basic Validation)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>No SQL/NoSQL injection payload accepted in API - Verify rule executes correctly under normal inputs</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TC_B031</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/points - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>TC_B032</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/rating - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TC_B033</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/badges - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>TC_B034</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on /notifications to recipient UID - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TC_B035</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Restrict write on /notifications to recipient UID - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>TC_B036</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Allow admin write on /notifications for all - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TC_B037</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Allow citizen create on /complaints - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>TC_B038</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Enforce citizenId matches auth.uid on /complaints creation - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TC_B039</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/status - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>TC_B040</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/assignedWorkerId - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TC_B041</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Block public write on /leaderboard - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>TC_B042</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Allow public read on /leaderboard - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TC_B043</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Block worker write on /workers/{otherId} - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>TC_B044</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on worker profile details to auth users - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TC_B045</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Block unauthenticated users from Firestore reads/writes - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>TC_B046</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved awards points - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TC_B047</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved updates leaderboard - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>TC_B048</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Award points function handles worker rating calculation - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TC_B049</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Rating calculation protects against division-by-zero - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>TC_B050</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: resolvedAt is after acceptedAt - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TC_B051</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: acceptedAt is after createdAt - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>TC_B052</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets assignedWorkerId - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TC_B053</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets status to In Progress - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>TC_B054</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Task rejection sets status back to In Progress - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TC_B055</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Auto-archive functions run on scheduled cron - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>TC_B056</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Verify complaint record requires mandatory title/description - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TC_B057</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Verify worker points count is non-negative - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>TC_B058</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Verify rating value is restricted between 1 and 5 - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TC_B059</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Firestore inputs sanitized for XSS/injection payloads - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>TC_B060</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Admin Context)</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>No SQL/NoSQL injection payload accepted in API - Verify rule handles admin override permissions correctly</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>TC_B061</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/points - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>TC_B062</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/rating - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>TC_B063</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/badges - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>TC_B064</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on /notifications to recipient UID - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>TC_B065</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Restrict write on /notifications to recipient UID - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>TC_B066</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Allow admin write on /notifications for all - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>TC_B067</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Allow citizen create on /complaints - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>TC_B068</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Enforce citizenId matches auth.uid on /complaints creation - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>TC_B069</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/status - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>TC_B070</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/assignedWorkerId - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>TC_B071</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Block public write on /leaderboard - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>TC_B072</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Allow public read on /leaderboard - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>TC_B073</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Block worker write on /workers/{otherId} - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>TC_B074</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on worker profile details to auth users - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>TC_B075</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Block unauthenticated users from Firestore reads/writes - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>TC_B076</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved awards points - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>TC_B077</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved updates leaderboard - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>TC_B078</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Award points function handles worker rating calculation - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>TC_B079</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Rating calculation protects against division-by-zero - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>TC_B080</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: resolvedAt is after acceptedAt - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>TC_B081</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: acceptedAt is after createdAt - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>TC_B082</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets assignedWorkerId - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>TC_B083</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets status to In Progress - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>TC_B084</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Task rejection sets status back to In Progress - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>TC_B085</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Auto-archive functions run on scheduled cron - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>TC_B086</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Verify complaint record requires mandatory title/description - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>TC_B087</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Verify worker points count is non-negative - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>TC_B088</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Verify rating value is restricted between 1 and 5 - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>TC_B089</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Firestore inputs sanitized for XSS/injection payloads - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>TC_B090</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Unauth Request)</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>No SQL/NoSQL injection payload accepted in API - Verify unauthenticated requests are rejected</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>TC_B091</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/points - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>TC_B092</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/rating - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>TC_B093</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/badges - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>TC_B094</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on /notifications to recipient UID - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>TC_B095</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Restrict write on /notifications to recipient UID - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>TC_B096</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Allow admin write on /notifications for all - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>TC_B097</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Allow citizen create on /complaints - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>TC_B098</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Enforce citizenId matches auth.uid on /complaints creation - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>TC_B099</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/status - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>TC_B100</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/assignedWorkerId - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>TC_B101</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Block public write on /leaderboard - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>TC_B102</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Allow public read on /leaderboard - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>TC_B103</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Block worker write on /workers/{otherId} - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>TC_B104</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on worker profile details to auth users - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>TC_B105</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>Block unauthenticated users from Firestore reads/writes - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>TC_B106</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved awards points - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>TC_B107</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved updates leaderboard - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>TC_B108</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Award points function handles worker rating calculation - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>TC_B109</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>Rating calculation protects against division-by-zero - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F110" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>TC_B110</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: resolvedAt is after acceptedAt - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>TC_B111</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: acceptedAt is after createdAt - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F112" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>TC_B112</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets assignedWorkerId - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>TC_B113</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets status to In Progress - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F114" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>TC_B114</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Task rejection sets status back to In Progress - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>TC_B115</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Auto-archive functions run on scheduled cron - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F116" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>TC_B116</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Verify complaint record requires mandatory title/description - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F117" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>TC_B117</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Verify worker points count is non-negative - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F118" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>TC_B118</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Verify rating value is restricted between 1 and 5 - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>TC_B119</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>Firestore inputs sanitized for XSS/injection payloads - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F120" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>TC_B120</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Malformed Payload)</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>No SQL/NoSQL injection payload accepted in API - Verify malformed json/payload formats are rejected</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>TC_B121</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/points - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F122" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>TC_B122</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/rating - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F123" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>TC_B123</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/badges - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F124" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>TC_B124</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on /notifications to recipient UID - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F125" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>TC_B125</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>Restrict write on /notifications to recipient UID - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F126" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>TC_B126</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>Allow admin write on /notifications for all - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F127" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>TC_B127</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>Allow citizen create on /complaints - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F128" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>TC_B128</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>Enforce citizenId matches auth.uid on /complaints creation - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F129" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>TC_B129</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/status - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F130" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>TC_B130</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/assignedWorkerId - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F131" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>TC_B131</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>Block public write on /leaderboard - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F132" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>TC_B132</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>Allow public read on /leaderboard - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F133" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>TC_B133</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>Block worker write on /workers/{otherId} - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F134" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>TC_B134</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on worker profile details to auth users - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F135" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>TC_B135</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>Block unauthenticated users from Firestore reads/writes - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F136" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>TC_B136</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved awards points - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F137" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>TC_B137</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved updates leaderboard - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F138" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>TC_B138</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>Award points function handles worker rating calculation - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F139" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>TC_B139</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>Rating calculation protects against division-by-zero - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F140" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>TC_B140</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: resolvedAt is after acceptedAt - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F141" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>TC_B141</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: acceptedAt is after createdAt - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F142" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>TC_B142</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets assignedWorkerId - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F143" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>TC_B143</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets status to In Progress - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F144" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>TC_B144</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>Task rejection sets status back to In Progress - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F145" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>TC_B145</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>Auto-archive functions run on scheduled cron - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F146" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>TC_B146</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>Verify complaint record requires mandatory title/description - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F147" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>TC_B147</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>Verify worker points count is non-negative - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F148" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>TC_B148</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>Verify rating value is restricted between 1 and 5 - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F149" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>TC_B149</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>Firestore inputs sanitized for XSS/injection payloads - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F150" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>TC_B150</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Boundary Values)</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>No SQL/NoSQL injection payload accepted in API - Verify limits like empty, extremely long strings, boundary values</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F151" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="20" customHeight="1">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>TC_B151</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Null Values)</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/points - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F152" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="20" customHeight="1">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>TC_B152</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Null Values)</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/rating - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F153" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="20" customHeight="1">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>TC_B153</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Null Values)</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/badges - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F154" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="20" customHeight="1">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>TC_B154</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Null Values)</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on /notifications to recipient UID - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F155" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>TC_B155</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Null Values)</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>Restrict write on /notifications to recipient UID - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D156" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F156" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="20" customHeight="1">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>TC_B156</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Null Values)</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>Allow admin write on /notifications for all - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D157" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F157" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="20" customHeight="1">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>TC_B157</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Null Values)</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>Allow citizen create on /complaints - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F158" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>TC_B158</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Null Values)</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>Enforce citizenId matches auth.uid on /complaints creation - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F159" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="20" customHeight="1">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>TC_B159</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Null Values)</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/status - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F160" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="20" customHeight="1">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>TC_B160</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Null Values)</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/assignedWorkerId - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F161" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="20" customHeight="1">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>TC_B161</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Null Values)</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>Block public write on /leaderboard - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F162" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="20" customHeight="1">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>TC_B162</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Null Values)</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>Allow public read on /leaderboard - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F163" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="20" customHeight="1">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>TC_B163</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Null Values)</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>Block worker write on /workers/{otherId} - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D164" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F164" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="20" customHeight="1">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>TC_B164</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Null Values)</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on worker profile details to auth users - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D165" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F165" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="20" customHeight="1">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>TC_B165</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Null Values)</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>Block unauthenticated users from Firestore reads/writes - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F166" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="20" customHeight="1">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>TC_B166</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Null Values)</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved awards points - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F167" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>TC_B167</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Null Values)</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved updates leaderboard - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F168" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>TC_B168</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Null Values)</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>Award points function handles worker rating calculation - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F169" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>TC_B169</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Null Values)</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>Rating calculation protects against division-by-zero - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F170" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>TC_B170</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Null Values)</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: resolvedAt is after acceptedAt - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F171" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="20" customHeight="1">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>TC_B171</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Null Values)</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: acceptedAt is after createdAt - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D172" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F172" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="20" customHeight="1">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>TC_B172</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Null Values)</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets assignedWorkerId - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F173" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="20" customHeight="1">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>TC_B173</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Null Values)</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets status to In Progress - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F174" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="20" customHeight="1">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>TC_B174</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Null Values)</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>Task rejection sets status back to In Progress - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D175" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F175" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>TC_B175</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Null Values)</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>Auto-archive functions run on scheduled cron - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F176" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="20" customHeight="1">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>TC_B176</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Null Values)</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>Verify complaint record requires mandatory title/description - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F177" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="20" customHeight="1">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>TC_B177</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Null Values)</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>Verify worker points count is non-negative - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F178" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="20" customHeight="1">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>TC_B178</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Null Values)</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>Verify rating value is restricted between 1 and 5 - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F179" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>TC_B179</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Null Values)</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>Firestore inputs sanitized for XSS/injection payloads - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F180" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="20" customHeight="1">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>TC_B180</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Null Values)</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>No SQL/NoSQL injection payload accepted in API - Verify missing properties/null values are rejected or fallback</t>
+        </is>
+      </c>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F181" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="20" customHeight="1">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>TC_B181</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/points - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F182" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="20" customHeight="1">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>TC_B182</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/rating - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D183" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F183" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="20" customHeight="1">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>TC_B183</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/badges - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F184" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="20" customHeight="1">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>TC_B184</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on /notifications to recipient UID - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D185" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E185" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F185" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="20" customHeight="1">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>TC_B185</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>Restrict write on /notifications to recipient UID - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F186" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="20" customHeight="1">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>TC_B186</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>Allow admin write on /notifications for all - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D187" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F187" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="20" customHeight="1">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>TC_B187</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>Allow citizen create on /complaints - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D188" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F188" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="20" customHeight="1">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>TC_B188</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>Enforce citizenId matches auth.uid on /complaints creation - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E189" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F189" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="20" customHeight="1">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>TC_B189</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/status - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F190" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>TC_B190</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/assignedWorkerId - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E191" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F191" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="20" customHeight="1">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>TC_B191</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>Block public write on /leaderboard - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D192" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F192" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="20" customHeight="1">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>TC_B192</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>Allow public read on /leaderboard - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D193" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E193" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F193" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="20" customHeight="1">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>TC_B193</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>Block worker write on /workers/{otherId} - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E194" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F194" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="20" customHeight="1">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>TC_B194</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on worker profile details to auth users - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D195" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E195" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F195" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="20" customHeight="1">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>TC_B195</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>Block unauthenticated users from Firestore reads/writes - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D196" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F196" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="20" customHeight="1">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>TC_B196</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved awards points - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D197" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F197" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="20" customHeight="1">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>TC_B197</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved updates leaderboard - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D198" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F198" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="20" customHeight="1">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>TC_B198</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>Award points function handles worker rating calculation - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D199" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E199" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F199" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="20" customHeight="1">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>TC_B199</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>Rating calculation protects against division-by-zero - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D200" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E200" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F200" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="20" customHeight="1">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>TC_B200</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: resolvedAt is after acceptedAt - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D201" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E201" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F201" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="20" customHeight="1">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>TC_B201</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: acceptedAt is after createdAt - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D202" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E202" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F202" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="20" customHeight="1">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>TC_B202</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets assignedWorkerId - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E203" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F203" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="20" customHeight="1">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>TC_B203</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets status to In Progress - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D204" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E204" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F204" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="20" customHeight="1">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>TC_B204</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>Task rejection sets status back to In Progress - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E205" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F205" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="20" customHeight="1">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>TC_B205</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>Auto-archive functions run on scheduled cron - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D206" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E206" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F206" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="20" customHeight="1">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>TC_B206</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>Verify complaint record requires mandatory title/description - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D207" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F207" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="20" customHeight="1">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>TC_B207</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>Verify worker points count is non-negative - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D208" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E208" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F208" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="20" customHeight="1">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>TC_B208</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>Verify rating value is restricted between 1 and 5 - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D209" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E209" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F209" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="20" customHeight="1">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>TC_B209</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>Firestore inputs sanitized for XSS/injection payloads - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D210" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E210" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F210" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="20" customHeight="1">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>TC_B210</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Transaction Safety)</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>No SQL/NoSQL injection payload accepted in API - Verify transaction atomic locking to prevent race conditions</t>
+        </is>
+      </c>
+      <c r="D211" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E211" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F211" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="20" customHeight="1">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>TC_B211</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/points - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D212" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E212" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F212" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="20" customHeight="1">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>TC_B212</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/rating - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D213" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F213" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="20" customHeight="1">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>TC_B213</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/badges - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D214" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E214" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F214" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="20" customHeight="1">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>TC_B214</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on /notifications to recipient UID - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D215" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E215" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F215" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="20" customHeight="1">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>TC_B215</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>Restrict write on /notifications to recipient UID - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D216" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E216" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F216" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="20" customHeight="1">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>TC_B216</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>Allow admin write on /notifications for all - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D217" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E217" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F217" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="20" customHeight="1">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>TC_B217</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>Allow citizen create on /complaints - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D218" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E218" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F218" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="20" customHeight="1">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>TC_B218</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>Enforce citizenId matches auth.uid on /complaints creation - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D219" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E219" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F219" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="20" customHeight="1">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>TC_B219</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/status - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D220" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E220" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F220" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="20" customHeight="1">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>TC_B220</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/assignedWorkerId - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D221" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E221" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F221" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="20" customHeight="1">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>TC_B221</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>Block public write on /leaderboard - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D222" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E222" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F222" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="20" customHeight="1">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>TC_B222</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>Allow public read on /leaderboard - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D223" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E223" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F223" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="20" customHeight="1">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>TC_B223</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>Block worker write on /workers/{otherId} - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D224" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E224" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F224" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="20" customHeight="1">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>TC_B224</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on worker profile details to auth users - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D225" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E225" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F225" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="20" customHeight="1">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>TC_B225</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>Block unauthenticated users from Firestore reads/writes - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D226" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E226" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F226" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="20" customHeight="1">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>TC_B226</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved awards points - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D227" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E227" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F227" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="20" customHeight="1">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>TC_B227</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved updates leaderboard - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D228" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E228" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F228" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="20" customHeight="1">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>TC_B228</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>Award points function handles worker rating calculation - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D229" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E229" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F229" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="20" customHeight="1">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>TC_B229</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>Rating calculation protects against division-by-zero - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D230" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E230" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F230" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="20" customHeight="1">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>TC_B230</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: resolvedAt is after acceptedAt - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D231" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E231" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F231" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="20" customHeight="1">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>TC_B231</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: acceptedAt is after createdAt - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D232" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E232" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F232" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="20" customHeight="1">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>TC_B232</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets assignedWorkerId - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D233" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E233" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F233" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="20" customHeight="1">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>TC_B233</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets status to In Progress - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D234" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E234" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F234" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="20" customHeight="1">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>TC_B234</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>Task rejection sets status back to In Progress - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D235" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E235" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F235" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="20" customHeight="1">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>TC_B235</t>
+        </is>
+      </c>
+      <c r="B236" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr">
+        <is>
+          <t>Auto-archive functions run on scheduled cron - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D236" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E236" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F236" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="20" customHeight="1">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>TC_B236</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>Verify complaint record requires mandatory title/description - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D237" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E237" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F237" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="20" customHeight="1">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>TC_B237</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>Verify worker points count is non-negative - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D238" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E238" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F238" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="20" customHeight="1">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>TC_B238</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>Verify rating value is restricted between 1 and 5 - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D239" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E239" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F239" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="20" customHeight="1">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>TC_B239</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>Firestore inputs sanitized for XSS/injection payloads - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D240" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E240" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F240" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="20" customHeight="1">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>TC_B240</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (CORS &amp; Headers)</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>No SQL/NoSQL injection payload accepted in API - Verify API requests enforce CORS rules and secure headers</t>
+        </is>
+      </c>
+      <c r="D241" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E241" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F241" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="20" customHeight="1">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>TC_B241</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/points - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D242" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E242" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F242" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="20" customHeight="1">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>TC_B242</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/rating - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D243" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E243" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F243" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="20" customHeight="1">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>TC_B243</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/badges - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D244" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E244" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F244" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="20" customHeight="1">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>TC_B244</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on /notifications to recipient UID - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D245" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E245" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F245" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="20" customHeight="1">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>TC_B245</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>Restrict write on /notifications to recipient UID - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D246" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E246" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F246" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="20" customHeight="1">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>TC_B246</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>Allow admin write on /notifications for all - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D247" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E247" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F247" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="20" customHeight="1">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>TC_B247</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>Allow citizen create on /complaints - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D248" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E248" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F248" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="20" customHeight="1">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>TC_B248</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>Enforce citizenId matches auth.uid on /complaints creation - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D249" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E249" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F249" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="20" customHeight="1">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>TC_B249</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/status - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D250" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E250" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F250" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="20" customHeight="1">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>TC_B250</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/assignedWorkerId - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D251" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E251" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F251" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="20" customHeight="1">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>TC_B251</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>Block public write on /leaderboard - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D252" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E252" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F252" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="20" customHeight="1">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>TC_B252</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="inlineStr">
+        <is>
+          <t>Allow public read on /leaderboard - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D253" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E253" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F253" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="20" customHeight="1">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>TC_B253</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>Block worker write on /workers/{otherId} - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D254" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E254" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F254" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="20" customHeight="1">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>TC_B254</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on worker profile details to auth users - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D255" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E255" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F255" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="20" customHeight="1">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>TC_B255</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>Block unauthenticated users from Firestore reads/writes - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D256" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E256" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F256" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="20" customHeight="1">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>TC_B256</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved awards points - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D257" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E257" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F257" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="20" customHeight="1">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>TC_B257</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved updates leaderboard - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D258" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E258" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F258" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="20" customHeight="1">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>TC_B258</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>Award points function handles worker rating calculation - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D259" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E259" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F259" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="20" customHeight="1">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>TC_B259</t>
+        </is>
+      </c>
+      <c r="B260" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C260" s="4" t="inlineStr">
+        <is>
+          <t>Rating calculation protects against division-by-zero - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D260" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E260" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F260" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="20" customHeight="1">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>TC_B260</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: resolvedAt is after acceptedAt - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D261" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E261" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F261" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="20" customHeight="1">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>TC_B261</t>
+        </is>
+      </c>
+      <c r="B262" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: acceptedAt is after createdAt - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D262" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E262" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F262" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="20" customHeight="1">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>TC_B262</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets assignedWorkerId - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D263" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E263" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F263" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="20" customHeight="1">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>TC_B263</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets status to In Progress - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D264" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E264" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F264" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="20" customHeight="1">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>TC_B264</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C265" s="4" t="inlineStr">
+        <is>
+          <t>Task rejection sets status back to In Progress - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D265" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E265" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F265" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="20" customHeight="1">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>TC_B265</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C266" s="4" t="inlineStr">
+        <is>
+          <t>Auto-archive functions run on scheduled cron - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D266" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E266" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F266" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="20" customHeight="1">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>TC_B266</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>Verify complaint record requires mandatory title/description - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D267" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E267" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F267" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="20" customHeight="1">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>TC_B267</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>Verify worker points count is non-negative - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D268" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E268" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F268" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="20" customHeight="1">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>TC_B268</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>Verify rating value is restricted between 1 and 5 - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D269" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E269" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F269" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="20" customHeight="1">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>TC_B269</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C270" s="4" t="inlineStr">
+        <is>
+          <t>Firestore inputs sanitized for XSS/injection payloads - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D270" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E270" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F270" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="20" customHeight="1">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>TC_B270</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Log Sanitization)</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>No SQL/NoSQL injection payload accepted in API - Verify system logs do not leak credentials or debug traces</t>
+        </is>
+      </c>
+      <c r="D271" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E271" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F271" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="20" customHeight="1">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>TC_B271</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/points - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D272" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E272" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F272" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="20" customHeight="1">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>TC_B272</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/rating - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D273" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E273" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F273" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="20" customHeight="1">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>TC_B273</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>Block client write on /workers/{workerId}/badges - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D274" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E274" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F274" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="20" customHeight="1">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>TC_B274</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on /notifications to recipient UID - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D275" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E275" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F275" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="20" customHeight="1">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>TC_B275</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C276" s="4" t="inlineStr">
+        <is>
+          <t>Restrict write on /notifications to recipient UID - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D276" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E276" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F276" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="20" customHeight="1">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>TC_B276</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="inlineStr">
+        <is>
+          <t>Allow admin write on /notifications for all - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D277" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E277" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F277" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="20" customHeight="1">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>TC_B277</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C278" s="4" t="inlineStr">
+        <is>
+          <t>Allow citizen create on /complaints - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D278" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E278" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F278" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="20" customHeight="1">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>TC_B278</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C279" s="4" t="inlineStr">
+        <is>
+          <t>Enforce citizenId matches auth.uid on /complaints creation - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D279" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E279" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F279" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="20" customHeight="1">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>TC_B279</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/status - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D280" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E280" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F280" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="20" customHeight="1">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t>TC_B280</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>Access Control (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>Block citizen edit on /complaints/{id}/assignedWorkerId - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D281" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E281" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F281" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="20" customHeight="1">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>TC_B281</t>
+        </is>
+      </c>
+      <c r="B282" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C282" s="4" t="inlineStr">
+        <is>
+          <t>Block public write on /leaderboard - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D282" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E282" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F282" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="20" customHeight="1">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>TC_B282</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr">
+        <is>
+          <t>Allow public read on /leaderboard - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D283" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E283" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F283" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="20" customHeight="1">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>TC_B283</t>
+        </is>
+      </c>
+      <c r="B284" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C284" s="4" t="inlineStr">
+        <is>
+          <t>Block worker write on /workers/{otherId} - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D284" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E284" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F284" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="20" customHeight="1">
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t>TC_B284</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C285" s="4" t="inlineStr">
+        <is>
+          <t>Restrict read on worker profile details to auth users - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D285" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E285" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F285" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="20" customHeight="1">
+      <c r="A286" s="3" t="inlineStr">
+        <is>
+          <t>TC_B285</t>
+        </is>
+      </c>
+      <c r="B286" s="4" t="inlineStr">
+        <is>
+          <t>Firestore Rules (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C286" s="4" t="inlineStr">
+        <is>
+          <t>Block unauthenticated users from Firestore reads/writes - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D286" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E286" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F286" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="20" customHeight="1">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>TC_B286</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C287" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved awards points - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D287" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E287" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F287" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="20" customHeight="1">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t>TC_B287</t>
+        </is>
+      </c>
+      <c r="B288" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C288" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on transition to Resolved updates leaderboard - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D288" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E288" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F288" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="20" customHeight="1">
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t>TC_B288</t>
+        </is>
+      </c>
+      <c r="B289" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C289" s="4" t="inlineStr">
+        <is>
+          <t>Award points function handles worker rating calculation - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D289" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E289" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F289" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="20" customHeight="1">
+      <c r="A290" s="3" t="inlineStr">
+        <is>
+          <t>TC_B289</t>
+        </is>
+      </c>
+      <c r="B290" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C290" s="4" t="inlineStr">
+        <is>
+          <t>Rating calculation protects against division-by-zero - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D290" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E290" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F290" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="20" customHeight="1">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
+          <t>TC_B290</t>
+        </is>
+      </c>
+      <c r="B291" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C291" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: resolvedAt is after acceptedAt - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D291" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E291" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F291" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="20" customHeight="1">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
+          <t>TC_B291</t>
+        </is>
+      </c>
+      <c r="B292" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
+          <t>Verify timeline: acceptedAt is after createdAt - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D292" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E292" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F292" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="20" customHeight="1">
+      <c r="A293" s="3" t="inlineStr">
+        <is>
+          <t>TC_B292</t>
+        </is>
+      </c>
+      <c r="B293" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C293" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets assignedWorkerId - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D293" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E293" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F293" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="20" customHeight="1">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t>TC_B293</t>
+        </is>
+      </c>
+      <c r="B294" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C294" s="4" t="inlineStr">
+        <is>
+          <t>Trigger on task acceptance sets status to In Progress - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D294" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E294" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F294" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="20" customHeight="1">
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t>TC_B294</t>
+        </is>
+      </c>
+      <c r="B295" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C295" s="4" t="inlineStr">
+        <is>
+          <t>Task rejection sets status back to In Progress - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D295" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E295" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F295" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="20" customHeight="1">
+      <c r="A296" s="3" t="inlineStr">
+        <is>
+          <t>TC_B295</t>
+        </is>
+      </c>
+      <c r="B296" s="4" t="inlineStr">
+        <is>
+          <t>State Machine (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C296" s="4" t="inlineStr">
+        <is>
+          <t>Auto-archive functions run on scheduled cron - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D296" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E296" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F296" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="20" customHeight="1">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
+          <t>TC_B296</t>
+        </is>
+      </c>
+      <c r="B297" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C297" s="4" t="inlineStr">
+        <is>
+          <t>Verify complaint record requires mandatory title/description - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D297" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E297" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F297" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="20" customHeight="1">
+      <c r="A298" s="3" t="inlineStr">
+        <is>
+          <t>TC_B297</t>
+        </is>
+      </c>
+      <c r="B298" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C298" s="4" t="inlineStr">
+        <is>
+          <t>Verify worker points count is non-negative - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D298" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E298" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F298" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="20" customHeight="1">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
+          <t>TC_B298</t>
+        </is>
+      </c>
+      <c r="B299" s="4" t="inlineStr">
+        <is>
+          <t>Data Validation (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>Verify rating value is restricted between 1 and 5 - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D299" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E299" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F299" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="20" customHeight="1">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t>TC_B299</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>Firestore inputs sanitized for XSS/injection payloads - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D300" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E300" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F300" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="20" customHeight="1">
+      <c r="A301" s="3" t="inlineStr">
+        <is>
+          <t>TC_B300</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="inlineStr">
+        <is>
+          <t>Security Audit (Rate Limiting)</t>
+        </is>
+      </c>
+      <c r="C301" s="4" t="inlineStr">
+        <is>
+          <t>No SQL/NoSQL injection payload accepted in API - Verify rate limits apply under heavy load</t>
+        </is>
+      </c>
+      <c r="D301" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E301" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F301" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="20" customHeight="1">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t>TC_B301</t>
+        </is>
+      </c>
+      <c r="B302" s="4" t="inlineStr">
+        <is>
+          <t>Data Leakage</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="inlineStr">
+        <is>
+          <t>Verify Firestore metadata fields do not leak in client responses</t>
+        </is>
+      </c>
+      <c r="D302" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E302" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F302" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="20" customHeight="1">
+      <c r="A303" s="3" t="inlineStr">
+        <is>
+          <t>TC_B302</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>Credential Rot</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="inlineStr">
+        <is>
+          <t>Verify expired service account private keys are rejected on API endpoints</t>
+        </is>
+      </c>
+      <c r="D303" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E303" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F303" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="20" customHeight="1">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>TC_B303</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
+          <t>Serverless Security</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="inlineStr">
+        <is>
+          <t>Verify Cloud Functions timeouts are restricted to prevent denial of wallet attacks</t>
+        </is>
+      </c>
+      <c r="D304" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E304" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F304" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="20" customHeight="1">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t>TC_B304</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
+          <t>Backup Integrity</t>
+        </is>
+      </c>
+      <c r="C305" s="4" t="inlineStr">
+        <is>
+          <t>Verify database backups are encrypted at rest with customer managed keys</t>
+        </is>
+      </c>
+      <c r="D305" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E305" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F305" s="8" t="inlineStr">
+        <is>
+          <t>09:26:19</t>
         </is>
       </c>
     </row>
